--- a/code/memoryTask/trialOrder.xlsx
+++ b/code/memoryTask/trialOrder.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Info1\Kaiser lab\New+project+Micha\images\LabelMe\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pep_wp4_eye_tracking\code\memoryTask\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA781E09-2093-4072-A306-7708FFFD3351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6DC775-7811-4E12-A02F-799317FBD053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,9 +562,6 @@
     <t>sun_auyiqnjooapfftxc.jpg</t>
   </si>
   <si>
-    <t>labelme_vtkizubrutntouq.jpg</t>
-  </si>
-  <si>
     <t>sun_aajwineqhytafdfq.jpg</t>
   </si>
   <si>
@@ -583,9 +580,6 @@
     <t>sun_aamdjwemxpmmtypi.jpg</t>
   </si>
   <si>
-    <t>sun_aamuzsrwpmctmkan.jpg</t>
-  </si>
-  <si>
     <t>sun_abapwbhyhkfixyex.jpg</t>
   </si>
   <si>
@@ -655,9 +649,6 @@
     <t>sun_abivdfzypgoaatlb.jpg</t>
   </si>
   <si>
-    <t>sun_aatcxjrhafurspvj.jpg</t>
-  </si>
-  <si>
     <t>sun_aafpallawmjtlxbq.jpg</t>
   </si>
   <si>
@@ -679,9 +670,6 @@
     <t>sun_aclxihxinvcqwpqb.jpg</t>
   </si>
   <si>
-    <t>sun_abrxlzzoqrtldkdw.jpg</t>
-  </si>
-  <si>
     <t>sun_aeckhfhauwooraxm.jpg</t>
   </si>
   <si>
@@ -769,9 +757,6 @@
     <t>sun_abktjgdhjcircubi.jpg</t>
   </si>
   <si>
-    <t>sun_aagxffpxwygavuss.jpg</t>
-  </si>
-  <si>
     <t>sun_auticobqsbwgoppi.jpg</t>
   </si>
   <si>
@@ -944,6 +929,21 @@
   </si>
   <si>
     <t>sun_aveufkcvojpcdova.jpg</t>
+  </si>
+  <si>
+    <t>sun_awwsahpstphbexsu.jpg</t>
+  </si>
+  <si>
+    <t>sun_atvabkwxtkmfrgpg.jpg</t>
+  </si>
+  <si>
+    <t>sun_apgsqzfknyrvgzzl.jpg</t>
+  </si>
+  <si>
+    <t>sun_albrprbpkugpwgvp.jpg</t>
+  </si>
+  <si>
+    <t>sun_anvnteddcdamdehd</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
         <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D2" t="s">
         <v>156</v>
@@ -1357,7 +1357,7 @@
         <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
         <v>157</v>
@@ -1371,7 +1371,7 @@
         <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="D4" t="s">
         <v>156</v>
@@ -1385,7 +1385,7 @@
         <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>179</v>
+        <v>303</v>
       </c>
       <c r="D5" t="s">
         <v>157</v>
@@ -1399,7 +1399,7 @@
         <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="D6" t="s">
         <v>156</v>
@@ -1413,7 +1413,7 @@
         <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
         <v>156</v>
@@ -1427,7 +1427,7 @@
         <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>252</v>
+        <v>289</v>
       </c>
       <c r="D8" t="s">
         <v>156</v>
@@ -1441,7 +1441,7 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>211</v>
+        <v>307</v>
       </c>
       <c r="D9" t="s">
         <v>157</v>
@@ -1455,7 +1455,7 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="D10" t="s">
         <v>157</v>
@@ -1469,7 +1469,7 @@
         <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>198</v>
+        <v>229</v>
       </c>
       <c r="D11" t="s">
         <v>157</v>
@@ -1483,7 +1483,7 @@
         <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="D12" t="s">
         <v>157</v>
@@ -1497,7 +1497,7 @@
         <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D13" t="s">
         <v>156</v>
@@ -1511,7 +1511,7 @@
         <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D14" t="s">
         <v>157</v>
@@ -1525,7 +1525,7 @@
         <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="D15" t="s">
         <v>156</v>
@@ -1539,7 +1539,7 @@
         <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -1553,7 +1553,7 @@
         <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -1567,7 +1567,7 @@
         <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D18" t="s">
         <v>156</v>
@@ -1581,7 +1581,7 @@
         <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -1595,7 +1595,7 @@
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D20" t="s">
         <v>156</v>
@@ -1609,7 +1609,7 @@
         <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>209</v>
+        <v>243</v>
       </c>
       <c r="D21" t="s">
         <v>156</v>
@@ -1623,7 +1623,7 @@
         <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="D22" t="s">
         <v>156</v>
@@ -1637,7 +1637,7 @@
         <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D23" t="s">
         <v>156</v>
@@ -1651,7 +1651,7 @@
         <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -1665,7 +1665,7 @@
         <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D25" t="s">
         <v>156</v>
@@ -1679,7 +1679,7 @@
         <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D26" t="s">
         <v>156</v>
@@ -1693,7 +1693,7 @@
         <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="D27" t="s">
         <v>157</v>
@@ -1707,7 +1707,7 @@
         <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D28" t="s">
         <v>157</v>
@@ -1721,7 +1721,7 @@
         <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D29" t="s">
         <v>157</v>
@@ -1735,7 +1735,7 @@
         <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>304</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -1749,7 +1749,7 @@
         <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>263</v>
+        <v>301</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -1763,7 +1763,7 @@
         <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -1777,7 +1777,7 @@
         <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>225</v>
+        <v>203</v>
       </c>
       <c r="D33" t="s">
         <v>156</v>
@@ -1791,7 +1791,7 @@
         <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D34" t="s">
         <v>157</v>
@@ -1805,7 +1805,7 @@
         <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>235</v>
+        <v>167</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -1819,7 +1819,7 @@
         <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -1833,7 +1833,7 @@
         <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -1847,7 +1847,7 @@
         <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D38" t="s">
         <v>157</v>
@@ -1861,7 +1861,7 @@
         <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>240</v>
+        <v>168</v>
       </c>
       <c r="D39" t="s">
         <v>157</v>
@@ -1875,7 +1875,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D40" t="s">
         <v>156</v>
@@ -1903,7 +1903,7 @@
         <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="D42" t="s">
         <v>157</v>
@@ -1931,7 +1931,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="D44" t="s">
         <v>157</v>
@@ -1945,7 +1945,7 @@
         <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>267</v>
+        <v>163</v>
       </c>
       <c r="D45" t="s">
         <v>156</v>
@@ -1959,7 +1959,7 @@
         <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>190</v>
+        <v>244</v>
       </c>
       <c r="D46" t="s">
         <v>156</v>
@@ -1973,7 +1973,7 @@
         <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="D47" t="s">
         <v>156</v>
@@ -1987,7 +1987,7 @@
         <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D48" t="s">
         <v>157</v>
@@ -2001,7 +2001,7 @@
         <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>205</v>
+        <v>290</v>
       </c>
       <c r="D49" t="s">
         <v>157</v>
@@ -2015,7 +2015,7 @@
         <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="D50" t="s">
         <v>156</v>
@@ -2029,7 +2029,7 @@
         <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="D51" t="s">
         <v>157</v>
@@ -2043,7 +2043,7 @@
         <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="D52" t="s">
         <v>156</v>
@@ -2057,7 +2057,7 @@
         <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D53" t="s">
         <v>156</v>
@@ -2071,7 +2071,7 @@
         <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2099,7 +2099,7 @@
         <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="D56" t="s">
         <v>156</v>
@@ -2113,7 +2113,7 @@
         <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>181</v>
+        <v>220</v>
       </c>
       <c r="D57" t="s">
         <v>156</v>
@@ -2127,7 +2127,7 @@
         <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D58" t="s">
         <v>157</v>
@@ -2141,7 +2141,7 @@
         <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="D59" t="s">
         <v>156</v>
@@ -2155,7 +2155,7 @@
         <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="D60" t="s">
         <v>157</v>
@@ -2169,7 +2169,7 @@
         <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>274</v>
+        <v>223</v>
       </c>
       <c r="D61" t="s">
         <v>157</v>
@@ -2183,7 +2183,7 @@
         <v>153</v>
       </c>
       <c r="C62" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="D62" t="s">
         <v>157</v>
@@ -2197,7 +2197,7 @@
         <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D63" t="s">
         <v>157</v>
@@ -2225,7 +2225,7 @@
         <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="D65" t="s">
         <v>157</v>
@@ -2239,7 +2239,7 @@
         <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="D66" t="s">
         <v>157</v>
@@ -2253,7 +2253,7 @@
         <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D67" t="s">
         <v>156</v>
@@ -2267,7 +2267,7 @@
         <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -2281,7 +2281,7 @@
         <v>153</v>
       </c>
       <c r="C69" t="s">
-        <v>246</v>
+        <v>173</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
@@ -2295,7 +2295,7 @@
         <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="D70" t="s">
         <v>157</v>
@@ -2309,7 +2309,7 @@
         <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>191</v>
+        <v>267</v>
       </c>
       <c r="D71" t="s">
         <v>156</v>
@@ -2323,7 +2323,7 @@
         <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D72" t="s">
         <v>157</v>
@@ -2337,7 +2337,7 @@
         <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="D73" t="s">
         <v>156</v>
@@ -2351,7 +2351,7 @@
         <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D74" t="s">
         <v>157</v>
@@ -2365,7 +2365,7 @@
         <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
         <v>157</v>
@@ -2393,7 +2393,7 @@
         <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="D77" t="s">
         <v>157</v>
@@ -2407,7 +2407,7 @@
         <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D78" t="s">
         <v>157</v>
@@ -2421,7 +2421,7 @@
         <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="D79" t="s">
         <v>157</v>
@@ -2435,7 +2435,7 @@
         <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="D80" t="s">
         <v>156</v>
@@ -2449,7 +2449,7 @@
         <v>153</v>
       </c>
       <c r="C81" t="s">
-        <v>210</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
         <v>156</v>
@@ -2463,7 +2463,7 @@
         <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D82" t="s">
         <v>156</v>
@@ -2477,7 +2477,7 @@
         <v>153</v>
       </c>
       <c r="C83" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="D83" t="s">
         <v>156</v>
@@ -2491,7 +2491,7 @@
         <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D84" t="s">
         <v>156</v>
@@ -2505,7 +2505,7 @@
         <v>153</v>
       </c>
       <c r="C85" t="s">
-        <v>281</v>
+        <v>247</v>
       </c>
       <c r="D85" t="s">
         <v>156</v>
@@ -2519,7 +2519,7 @@
         <v>153</v>
       </c>
       <c r="C86" t="s">
-        <v>219</v>
+        <v>172</v>
       </c>
       <c r="D86" t="s">
         <v>157</v>
@@ -2533,7 +2533,7 @@
         <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="D87" t="s">
         <v>157</v>
@@ -2547,7 +2547,7 @@
         <v>153</v>
       </c>
       <c r="C88" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -2561,7 +2561,7 @@
         <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D89" t="s">
         <v>157</v>
@@ -2575,7 +2575,7 @@
         <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>173</v>
+        <v>222</v>
       </c>
       <c r="D90" t="s">
         <v>157</v>
@@ -2589,7 +2589,7 @@
         <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="D91" t="s">
         <v>157</v>
@@ -2603,7 +2603,7 @@
         <v>153</v>
       </c>
       <c r="C92" t="s">
-        <v>164</v>
+        <v>186</v>
       </c>
       <c r="D92" t="s">
         <v>157</v>
@@ -2631,7 +2631,7 @@
         <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="D94" t="s">
         <v>156</v>
@@ -2645,7 +2645,7 @@
         <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D95" t="s">
         <v>157</v>
@@ -2659,7 +2659,7 @@
         <v>153</v>
       </c>
       <c r="C96" t="s">
-        <v>162</v>
+        <v>195</v>
       </c>
       <c r="D96" t="s">
         <v>156</v>
@@ -2673,7 +2673,7 @@
         <v>152</v>
       </c>
       <c r="C97" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D97" t="s">
         <v>156</v>
@@ -2687,7 +2687,7 @@
         <v>152</v>
       </c>
       <c r="C98" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -2715,7 +2715,7 @@
         <v>152</v>
       </c>
       <c r="C100" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="D100" t="s">
         <v>157</v>
@@ -2729,7 +2729,7 @@
         <v>153</v>
       </c>
       <c r="C101" t="s">
-        <v>245</v>
+        <v>178</v>
       </c>
       <c r="D101" t="s">
         <v>157</v>
@@ -2743,7 +2743,7 @@
         <v>152</v>
       </c>
       <c r="C102" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D102" t="s">
         <v>157</v>
@@ -2757,7 +2757,7 @@
         <v>153</v>
       </c>
       <c r="C103" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="D103" t="s">
         <v>156</v>
@@ -2771,7 +2771,7 @@
         <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D104" t="s">
         <v>156</v>
@@ -2785,7 +2785,7 @@
         <v>153</v>
       </c>
       <c r="C105" t="s">
-        <v>227</v>
+        <v>159</v>
       </c>
       <c r="D105" t="s">
         <v>156</v>
@@ -2799,7 +2799,7 @@
         <v>153</v>
       </c>
       <c r="C106" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D106" t="s">
         <v>156</v>
@@ -2813,7 +2813,7 @@
         <v>152</v>
       </c>
       <c r="C107" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D107" t="s">
         <v>156</v>
@@ -2827,7 +2827,7 @@
         <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D108" t="s">
         <v>157</v>
@@ -2841,7 +2841,7 @@
         <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -2855,7 +2855,7 @@
         <v>153</v>
       </c>
       <c r="C110" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="D110" t="s">
         <v>156</v>
@@ -2869,7 +2869,7 @@
         <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D111" t="s">
         <v>157</v>
@@ -2883,7 +2883,7 @@
         <v>152</v>
       </c>
       <c r="C112" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D112" t="s">
         <v>157</v>
@@ -2897,7 +2897,7 @@
         <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="D113" t="s">
         <v>157</v>
@@ -2911,7 +2911,7 @@
         <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D114" t="s">
         <v>157</v>
@@ -2925,7 +2925,7 @@
         <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D115" t="s">
         <v>157</v>
@@ -2939,7 +2939,7 @@
         <v>153</v>
       </c>
       <c r="C116" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="D116" t="s">
         <v>157</v>
@@ -2953,7 +2953,7 @@
         <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D117" t="s">
         <v>157</v>
@@ -2967,7 +2967,7 @@
         <v>153</v>
       </c>
       <c r="C118" t="s">
-        <v>167</v>
+        <v>221</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -2981,7 +2981,7 @@
         <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="D119" t="s">
         <v>157</v>
@@ -2995,7 +2995,7 @@
         <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="D120" t="s">
         <v>156</v>
@@ -3009,7 +3009,7 @@
         <v>153</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="D121" t="s">
         <v>157</v>
@@ -3023,7 +3023,7 @@
         <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D122" t="s">
         <v>156</v>
@@ -3037,7 +3037,7 @@
         <v>153</v>
       </c>
       <c r="C123" t="s">
-        <v>204</v>
+        <v>306</v>
       </c>
       <c r="D123" t="s">
         <v>156</v>
@@ -3051,7 +3051,7 @@
         <v>153</v>
       </c>
       <c r="C124" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="D124" t="s">
         <v>156</v>
@@ -3065,7 +3065,7 @@
         <v>152</v>
       </c>
       <c r="C125" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="D125" t="s">
         <v>157</v>
@@ -3079,7 +3079,7 @@
         <v>152</v>
       </c>
       <c r="C126" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D126" t="s">
         <v>157</v>
@@ -3093,7 +3093,7 @@
         <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -3107,7 +3107,7 @@
         <v>152</v>
       </c>
       <c r="C128" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D128" t="s">
         <v>156</v>
@@ -3121,7 +3121,7 @@
         <v>153</v>
       </c>
       <c r="C129" t="s">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="D129" t="s">
         <v>156</v>
@@ -3135,7 +3135,7 @@
         <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="D130" t="s">
         <v>156</v>
@@ -3149,7 +3149,7 @@
         <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>187</v>
+        <v>164</v>
       </c>
       <c r="D131" t="s">
         <v>157</v>
@@ -3163,7 +3163,7 @@
         <v>152</v>
       </c>
       <c r="C132" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D132" t="s">
         <v>156</v>
@@ -3177,7 +3177,7 @@
         <v>152</v>
       </c>
       <c r="C133" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D133" t="s">
         <v>157</v>
@@ -3191,7 +3191,7 @@
         <v>152</v>
       </c>
       <c r="C134" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D134" t="s">
         <v>157</v>
@@ -3205,7 +3205,7 @@
         <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
       <c r="D135" t="s">
         <v>156</v>
@@ -3219,7 +3219,7 @@
         <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="D136" t="s">
         <v>156</v>
@@ -3233,7 +3233,7 @@
         <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>192</v>
+        <v>215</v>
       </c>
       <c r="D137" t="s">
         <v>157</v>
@@ -3247,7 +3247,7 @@
         <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D138" t="s">
         <v>156</v>
@@ -3261,7 +3261,7 @@
         <v>153</v>
       </c>
       <c r="C139" t="s">
-        <v>175</v>
+        <v>196</v>
       </c>
       <c r="D139" t="s">
         <v>156</v>
@@ -3275,7 +3275,7 @@
         <v>152</v>
       </c>
       <c r="C140" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D140" t="s">
         <v>157</v>
@@ -3289,7 +3289,7 @@
         <v>152</v>
       </c>
       <c r="C141" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D141" t="s">
         <v>156</v>
@@ -3303,7 +3303,7 @@
         <v>153</v>
       </c>
       <c r="C142" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D142" t="s">
         <v>156</v>
@@ -3331,7 +3331,7 @@
         <v>153</v>
       </c>
       <c r="C144" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="D144" t="s">
         <v>157</v>
@@ -3345,7 +3345,7 @@
         <v>152</v>
       </c>
       <c r="C145" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D145" t="s">
         <v>156</v>
@@ -3359,7 +3359,7 @@
         <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>188</v>
+        <v>234</v>
       </c>
       <c r="D146" t="s">
         <v>156</v>
@@ -3373,7 +3373,7 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="D147" t="s">
         <v>156</v>
@@ -3387,7 +3387,7 @@
         <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>306</v>
+        <v>288</v>
       </c>
       <c r="D148" t="s">
         <v>157</v>
@@ -3401,7 +3401,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D149" t="s">
         <v>156</v>
@@ -3415,7 +3415,7 @@
         <v>152</v>
       </c>
       <c r="C150" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="D150" t="s">
         <v>157</v>
@@ -3429,7 +3429,7 @@
         <v>153</v>
       </c>
       <c r="C151" t="s">
-        <v>226</v>
+        <v>177</v>
       </c>
       <c r="D151" t="s">
         <v>156</v>

--- a/code/memoryTask/trialOrder.xlsx
+++ b/code/memoryTask/trialOrder.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\pep_wp4_eye_tracking\code\memoryTask\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Info1\Kaiser lab\New+project+Micha\images\LabelMe\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F6DC775-7811-4E12-A02F-799317FBD053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C4CB0D-AA22-40B9-966A-A06B61C4CB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="804" yWindow="528" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -649,6 +649,9 @@
     <t>sun_abivdfzypgoaatlb.jpg</t>
   </si>
   <si>
+    <t>sun_aatcxjrhafurspvj.jpg</t>
+  </si>
+  <si>
     <t>sun_aafpallawmjtlxbq.jpg</t>
   </si>
   <si>
@@ -941,9 +944,6 @@
   </si>
   <si>
     <t>sun_albrprbpkugpwgvp.jpg</t>
-  </si>
-  <si>
-    <t>sun_anvnteddcdamdehd</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1357,7 @@
         <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D3" t="s">
         <v>157</v>
@@ -1385,7 +1385,7 @@
         <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D5" t="s">
         <v>157</v>
@@ -1399,7 +1399,7 @@
         <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
         <v>156</v>
@@ -1413,7 +1413,7 @@
         <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D7" t="s">
         <v>156</v>
@@ -1427,7 +1427,7 @@
         <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D8" t="s">
         <v>156</v>
@@ -1441,7 +1441,7 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>307</v>
+        <v>209</v>
       </c>
       <c r="D9" t="s">
         <v>157</v>
@@ -1469,7 +1469,7 @@
         <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
         <v>157</v>
@@ -1497,7 +1497,7 @@
         <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D13" t="s">
         <v>156</v>
@@ -1511,7 +1511,7 @@
         <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D14" t="s">
         <v>157</v>
@@ -1525,7 +1525,7 @@
         <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D15" t="s">
         <v>156</v>
@@ -1539,7 +1539,7 @@
         <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -1553,7 +1553,7 @@
         <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -1581,7 +1581,7 @@
         <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -1595,7 +1595,7 @@
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D20" t="s">
         <v>156</v>
@@ -1609,7 +1609,7 @@
         <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D21" t="s">
         <v>156</v>
@@ -1637,7 +1637,7 @@
         <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
         <v>156</v>
@@ -1651,7 +1651,7 @@
         <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -1665,7 +1665,7 @@
         <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
         <v>156</v>
@@ -1679,7 +1679,7 @@
         <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D26" t="s">
         <v>156</v>
@@ -1693,7 +1693,7 @@
         <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="D27" t="s">
         <v>157</v>
@@ -1707,7 +1707,7 @@
         <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="D28" t="s">
         <v>157</v>
@@ -1721,7 +1721,7 @@
         <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D29" t="s">
         <v>157</v>
@@ -1735,7 +1735,7 @@
         <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -1749,7 +1749,7 @@
         <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -1763,7 +1763,7 @@
         <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -1833,7 +1833,7 @@
         <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -1875,7 +1875,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D40" t="s">
         <v>156</v>
@@ -1903,7 +1903,7 @@
         <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D42" t="s">
         <v>157</v>
@@ -1931,7 +1931,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D44" t="s">
         <v>157</v>
@@ -1959,7 +1959,7 @@
         <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D46" t="s">
         <v>156</v>
@@ -1973,7 +1973,7 @@
         <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D47" t="s">
         <v>156</v>
@@ -1987,7 +1987,7 @@
         <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="D48" t="s">
         <v>157</v>
@@ -2001,7 +2001,7 @@
         <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D49" t="s">
         <v>157</v>
@@ -2015,7 +2015,7 @@
         <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D50" t="s">
         <v>156</v>
@@ -2043,7 +2043,7 @@
         <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D52" t="s">
         <v>156</v>
@@ -2057,7 +2057,7 @@
         <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D53" t="s">
         <v>156</v>
@@ -2099,7 +2099,7 @@
         <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D56" t="s">
         <v>156</v>
@@ -2113,7 +2113,7 @@
         <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D57" t="s">
         <v>156</v>
@@ -2127,7 +2127,7 @@
         <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D58" t="s">
         <v>157</v>
@@ -2141,7 +2141,7 @@
         <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D59" t="s">
         <v>156</v>
@@ -2155,7 +2155,7 @@
         <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D60" t="s">
         <v>157</v>
@@ -2169,7 +2169,7 @@
         <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D61" t="s">
         <v>157</v>
@@ -2197,7 +2197,7 @@
         <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D63" t="s">
         <v>157</v>
@@ -2253,7 +2253,7 @@
         <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D67" t="s">
         <v>156</v>
@@ -2267,7 +2267,7 @@
         <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -2295,7 +2295,7 @@
         <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
         <v>157</v>
@@ -2309,7 +2309,7 @@
         <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D71" t="s">
         <v>156</v>
@@ -2323,7 +2323,7 @@
         <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="D72" t="s">
         <v>157</v>
@@ -2365,7 +2365,7 @@
         <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D75" t="s">
         <v>157</v>
@@ -2421,7 +2421,7 @@
         <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D79" t="s">
         <v>157</v>
@@ -2435,7 +2435,7 @@
         <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D80" t="s">
         <v>156</v>
@@ -2449,7 +2449,7 @@
         <v>153</v>
       </c>
       <c r="C81" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D81" t="s">
         <v>156</v>
@@ -2463,7 +2463,7 @@
         <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D82" t="s">
         <v>156</v>
@@ -2491,7 +2491,7 @@
         <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D84" t="s">
         <v>156</v>
@@ -2505,7 +2505,7 @@
         <v>153</v>
       </c>
       <c r="C85" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D85" t="s">
         <v>156</v>
@@ -2533,7 +2533,7 @@
         <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D87" t="s">
         <v>157</v>
@@ -2561,7 +2561,7 @@
         <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="D89" t="s">
         <v>157</v>
@@ -2575,7 +2575,7 @@
         <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="D90" t="s">
         <v>157</v>
@@ -2631,7 +2631,7 @@
         <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D94" t="s">
         <v>156</v>
@@ -2687,7 +2687,7 @@
         <v>152</v>
       </c>
       <c r="C98" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -2715,7 +2715,7 @@
         <v>152</v>
       </c>
       <c r="C100" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="D100" t="s">
         <v>157</v>
@@ -2743,7 +2743,7 @@
         <v>152</v>
       </c>
       <c r="C102" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D102" t="s">
         <v>157</v>
@@ -2799,7 +2799,7 @@
         <v>153</v>
       </c>
       <c r="C106" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D106" t="s">
         <v>156</v>
@@ -2813,7 +2813,7 @@
         <v>152</v>
       </c>
       <c r="C107" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D107" t="s">
         <v>156</v>
@@ -2827,7 +2827,7 @@
         <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D108" t="s">
         <v>157</v>
@@ -2841,7 +2841,7 @@
         <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -2869,7 +2869,7 @@
         <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D111" t="s">
         <v>157</v>
@@ -2883,7 +2883,7 @@
         <v>152</v>
       </c>
       <c r="C112" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="D112" t="s">
         <v>157</v>
@@ -2897,7 +2897,7 @@
         <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D113" t="s">
         <v>157</v>
@@ -2911,7 +2911,7 @@
         <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="D114" t="s">
         <v>157</v>
@@ -2925,7 +2925,7 @@
         <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D115" t="s">
         <v>157</v>
@@ -2939,7 +2939,7 @@
         <v>153</v>
       </c>
       <c r="C116" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D116" t="s">
         <v>157</v>
@@ -2953,7 +2953,7 @@
         <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D117" t="s">
         <v>157</v>
@@ -2967,7 +2967,7 @@
         <v>153</v>
       </c>
       <c r="C118" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -2981,7 +2981,7 @@
         <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D119" t="s">
         <v>157</v>
@@ -2995,7 +2995,7 @@
         <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D120" t="s">
         <v>156</v>
@@ -3009,7 +3009,7 @@
         <v>153</v>
       </c>
       <c r="C121" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="D121" t="s">
         <v>157</v>
@@ -3023,7 +3023,7 @@
         <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D122" t="s">
         <v>156</v>
@@ -3037,7 +3037,7 @@
         <v>153</v>
       </c>
       <c r="C123" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D123" t="s">
         <v>156</v>
@@ -3065,7 +3065,7 @@
         <v>152</v>
       </c>
       <c r="C125" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D125" t="s">
         <v>157</v>
@@ -3093,7 +3093,7 @@
         <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -3107,7 +3107,7 @@
         <v>152</v>
       </c>
       <c r="C128" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D128" t="s">
         <v>156</v>
@@ -3121,7 +3121,7 @@
         <v>153</v>
       </c>
       <c r="C129" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D129" t="s">
         <v>156</v>
@@ -3135,7 +3135,7 @@
         <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D130" t="s">
         <v>156</v>
@@ -3163,7 +3163,7 @@
         <v>152</v>
       </c>
       <c r="C132" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D132" t="s">
         <v>156</v>
@@ -3177,7 +3177,7 @@
         <v>152</v>
       </c>
       <c r="C133" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D133" t="s">
         <v>157</v>
@@ -3219,7 +3219,7 @@
         <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D136" t="s">
         <v>156</v>
@@ -3233,7 +3233,7 @@
         <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D137" t="s">
         <v>157</v>
@@ -3247,7 +3247,7 @@
         <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D138" t="s">
         <v>156</v>
@@ -3275,7 +3275,7 @@
         <v>152</v>
       </c>
       <c r="C140" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D140" t="s">
         <v>157</v>
@@ -3289,7 +3289,7 @@
         <v>152</v>
       </c>
       <c r="C141" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D141" t="s">
         <v>156</v>
@@ -3303,7 +3303,7 @@
         <v>153</v>
       </c>
       <c r="C142" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D142" t="s">
         <v>156</v>
@@ -3317,7 +3317,7 @@
         <v>153</v>
       </c>
       <c r="C143" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D143" t="s">
         <v>157</v>
@@ -3345,7 +3345,7 @@
         <v>152</v>
       </c>
       <c r="C145" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D145" t="s">
         <v>156</v>
@@ -3359,7 +3359,7 @@
         <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D146" t="s">
         <v>156</v>
@@ -3373,7 +3373,7 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D147" t="s">
         <v>156</v>
@@ -3387,7 +3387,7 @@
         <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D148" t="s">
         <v>157</v>
@@ -3401,7 +3401,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D149" t="s">
         <v>156</v>
@@ -3415,7 +3415,7 @@
         <v>152</v>
       </c>
       <c r="C150" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D150" t="s">
         <v>157</v>

--- a/code/memoryTask/trialOrder.xlsx
+++ b/code/memoryTask/trialOrder.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Info1\Kaiser lab\New+project+Micha\images\LabelMe\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C4CB0D-AA22-40B9-966A-A06B61C4CB82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBDBFE8-F78C-4B04-962D-0ADE91A1B21D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="804" yWindow="528" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -649,9 +649,6 @@
     <t>sun_abivdfzypgoaatlb.jpg</t>
   </si>
   <si>
-    <t>sun_aatcxjrhafurspvj.jpg</t>
-  </si>
-  <si>
     <t>sun_aafpallawmjtlxbq.jpg</t>
   </si>
   <si>
@@ -944,6 +941,9 @@
   </si>
   <si>
     <t>sun_albrprbpkugpwgvp.jpg</t>
+  </si>
+  <si>
+    <t>sun_anvnteddcdamdehd.jpg</t>
   </si>
 </sst>
 </file>
@@ -1343,7 +1343,7 @@
         <v>152</v>
       </c>
       <c r="C2" t="s">
-        <v>204</v>
+        <v>300</v>
       </c>
       <c r="D2" t="s">
         <v>156</v>
@@ -1357,7 +1357,7 @@
         <v>152</v>
       </c>
       <c r="C3" t="s">
-        <v>246</v>
+        <v>291</v>
       </c>
       <c r="D3" t="s">
         <v>157</v>
@@ -1371,7 +1371,7 @@
         <v>153</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D4" t="s">
         <v>156</v>
@@ -1385,7 +1385,7 @@
         <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>304</v>
+        <v>184</v>
       </c>
       <c r="D5" t="s">
         <v>157</v>
@@ -1399,7 +1399,7 @@
         <v>153</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D6" t="s">
         <v>156</v>
@@ -1413,7 +1413,7 @@
         <v>152</v>
       </c>
       <c r="C7" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="D7" t="s">
         <v>156</v>
@@ -1427,7 +1427,7 @@
         <v>153</v>
       </c>
       <c r="C8" t="s">
-        <v>290</v>
+        <v>210</v>
       </c>
       <c r="D8" t="s">
         <v>156</v>
@@ -1441,7 +1441,7 @@
         <v>152</v>
       </c>
       <c r="C9" t="s">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
         <v>157</v>
@@ -1455,7 +1455,7 @@
         <v>153</v>
       </c>
       <c r="C10" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
       <c r="D10" t="s">
         <v>157</v>
@@ -1469,7 +1469,7 @@
         <v>153</v>
       </c>
       <c r="C11" t="s">
-        <v>230</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
         <v>157</v>
@@ -1483,7 +1483,7 @@
         <v>153</v>
       </c>
       <c r="C12" t="s">
-        <v>189</v>
+        <v>167</v>
       </c>
       <c r="D12" t="s">
         <v>157</v>
@@ -1497,7 +1497,7 @@
         <v>152</v>
       </c>
       <c r="C13" t="s">
-        <v>249</v>
+        <v>268</v>
       </c>
       <c r="D13" t="s">
         <v>156</v>
@@ -1511,7 +1511,7 @@
         <v>152</v>
       </c>
       <c r="C14" t="s">
-        <v>250</v>
+        <v>205</v>
       </c>
       <c r="D14" t="s">
         <v>157</v>
@@ -1525,7 +1525,7 @@
         <v>153</v>
       </c>
       <c r="C15" t="s">
-        <v>241</v>
+        <v>267</v>
       </c>
       <c r="D15" t="s">
         <v>156</v>
@@ -1539,7 +1539,7 @@
         <v>152</v>
       </c>
       <c r="C16" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
         <v>156</v>
@@ -1553,7 +1553,7 @@
         <v>152</v>
       </c>
       <c r="C17" t="s">
-        <v>252</v>
+        <v>204</v>
       </c>
       <c r="D17" t="s">
         <v>157</v>
@@ -1567,7 +1567,7 @@
         <v>152</v>
       </c>
       <c r="C18" t="s">
-        <v>205</v>
+        <v>275</v>
       </c>
       <c r="D18" t="s">
         <v>156</v>
@@ -1581,7 +1581,7 @@
         <v>152</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>166</v>
       </c>
       <c r="D19" t="s">
         <v>156</v>
@@ -1595,7 +1595,7 @@
         <v>152</v>
       </c>
       <c r="C20" t="s">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="D20" t="s">
         <v>156</v>
@@ -1609,7 +1609,7 @@
         <v>153</v>
       </c>
       <c r="C21" t="s">
-        <v>244</v>
+        <v>202</v>
       </c>
       <c r="D21" t="s">
         <v>156</v>
@@ -1623,7 +1623,7 @@
         <v>153</v>
       </c>
       <c r="C22" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="D22" t="s">
         <v>156</v>
@@ -1637,7 +1637,7 @@
         <v>152</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>194</v>
       </c>
       <c r="D23" t="s">
         <v>156</v>
@@ -1651,7 +1651,7 @@
         <v>152</v>
       </c>
       <c r="C24" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="D24" t="s">
         <v>156</v>
@@ -1665,7 +1665,7 @@
         <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="D25" t="s">
         <v>156</v>
@@ -1679,7 +1679,7 @@
         <v>152</v>
       </c>
       <c r="C26" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D26" t="s">
         <v>156</v>
@@ -1693,7 +1693,7 @@
         <v>153</v>
       </c>
       <c r="C27" t="s">
-        <v>225</v>
+        <v>244</v>
       </c>
       <c r="D27" t="s">
         <v>157</v>
@@ -1707,7 +1707,7 @@
         <v>153</v>
       </c>
       <c r="C28" t="s">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="D28" t="s">
         <v>157</v>
@@ -1721,7 +1721,7 @@
         <v>152</v>
       </c>
       <c r="C29" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="D29" t="s">
         <v>157</v>
@@ -1735,7 +1735,7 @@
         <v>153</v>
       </c>
       <c r="C30" t="s">
-        <v>305</v>
+        <v>159</v>
       </c>
       <c r="D30" t="s">
         <v>157</v>
@@ -1749,7 +1749,7 @@
         <v>153</v>
       </c>
       <c r="C31" t="s">
-        <v>302</v>
+        <v>269</v>
       </c>
       <c r="D31" t="s">
         <v>156</v>
@@ -1763,7 +1763,7 @@
         <v>152</v>
       </c>
       <c r="C32" t="s">
-        <v>260</v>
+        <v>293</v>
       </c>
       <c r="D32" t="s">
         <v>157</v>
@@ -1777,7 +1777,7 @@
         <v>153</v>
       </c>
       <c r="C33" t="s">
-        <v>203</v>
+        <v>162</v>
       </c>
       <c r="D33" t="s">
         <v>156</v>
@@ -1791,7 +1791,7 @@
         <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>190</v>
       </c>
       <c r="D34" t="s">
         <v>157</v>
@@ -1805,7 +1805,7 @@
         <v>153</v>
       </c>
       <c r="C35" t="s">
-        <v>167</v>
+        <v>215</v>
       </c>
       <c r="D35" t="s">
         <v>156</v>
@@ -1819,7 +1819,7 @@
         <v>152</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="D36" t="s">
         <v>157</v>
@@ -1833,7 +1833,7 @@
         <v>152</v>
       </c>
       <c r="C37" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D37" t="s">
         <v>157</v>
@@ -1847,7 +1847,7 @@
         <v>153</v>
       </c>
       <c r="C38" t="s">
-        <v>187</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
         <v>157</v>
@@ -1861,7 +1861,7 @@
         <v>153</v>
       </c>
       <c r="C39" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="D39" t="s">
         <v>157</v>
@@ -1875,7 +1875,7 @@
         <v>152</v>
       </c>
       <c r="C40" t="s">
-        <v>240</v>
+        <v>160</v>
       </c>
       <c r="D40" t="s">
         <v>156</v>
@@ -1889,7 +1889,7 @@
         <v>152</v>
       </c>
       <c r="C41" t="s">
-        <v>174</v>
+        <v>246</v>
       </c>
       <c r="D41" t="s">
         <v>156</v>
@@ -1903,7 +1903,7 @@
         <v>153</v>
       </c>
       <c r="C42" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D42" t="s">
         <v>157</v>
@@ -1917,7 +1917,7 @@
         <v>152</v>
       </c>
       <c r="C43" t="s">
-        <v>171</v>
+        <v>277</v>
       </c>
       <c r="D43" t="s">
         <v>156</v>
@@ -1931,7 +1931,7 @@
         <v>152</v>
       </c>
       <c r="C44" t="s">
-        <v>262</v>
+        <v>239</v>
       </c>
       <c r="D44" t="s">
         <v>157</v>
@@ -1945,7 +1945,7 @@
         <v>153</v>
       </c>
       <c r="C45" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="D45" t="s">
         <v>156</v>
@@ -1959,7 +1959,7 @@
         <v>153</v>
       </c>
       <c r="C46" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D46" t="s">
         <v>156</v>
@@ -1973,7 +1973,7 @@
         <v>152</v>
       </c>
       <c r="C47" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="D47" t="s">
         <v>156</v>
@@ -1987,7 +1987,7 @@
         <v>152</v>
       </c>
       <c r="C48" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D48" t="s">
         <v>157</v>
@@ -2001,7 +2001,7 @@
         <v>153</v>
       </c>
       <c r="C49" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
       <c r="D49" t="s">
         <v>157</v>
@@ -2015,7 +2015,7 @@
         <v>152</v>
       </c>
       <c r="C50" t="s">
-        <v>266</v>
+        <v>287</v>
       </c>
       <c r="D50" t="s">
         <v>156</v>
@@ -2029,7 +2029,7 @@
         <v>153</v>
       </c>
       <c r="C51" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="D51" t="s">
         <v>157</v>
@@ -2043,7 +2043,7 @@
         <v>152</v>
       </c>
       <c r="C52" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D52" t="s">
         <v>156</v>
@@ -2057,7 +2057,7 @@
         <v>153</v>
       </c>
       <c r="C53" t="s">
-        <v>275</v>
+        <v>301</v>
       </c>
       <c r="D53" t="s">
         <v>156</v>
@@ -2071,7 +2071,7 @@
         <v>153</v>
       </c>
       <c r="C54" t="s">
-        <v>190</v>
+        <v>236</v>
       </c>
       <c r="D54" t="s">
         <v>156</v>
@@ -2085,7 +2085,7 @@
         <v>152</v>
       </c>
       <c r="C55" t="s">
-        <v>169</v>
+        <v>201</v>
       </c>
       <c r="D55" t="s">
         <v>156</v>
@@ -2099,7 +2099,7 @@
         <v>153</v>
       </c>
       <c r="C56" t="s">
-        <v>215</v>
+        <v>289</v>
       </c>
       <c r="D56" t="s">
         <v>156</v>
@@ -2113,7 +2113,7 @@
         <v>153</v>
       </c>
       <c r="C57" t="s">
-        <v>221</v>
+        <v>164</v>
       </c>
       <c r="D57" t="s">
         <v>156</v>
@@ -2127,7 +2127,7 @@
         <v>152</v>
       </c>
       <c r="C58" t="s">
-        <v>233</v>
+        <v>302</v>
       </c>
       <c r="D58" t="s">
         <v>157</v>
@@ -2141,7 +2141,7 @@
         <v>152</v>
       </c>
       <c r="C59" t="s">
-        <v>269</v>
+        <v>298</v>
       </c>
       <c r="D59" t="s">
         <v>156</v>
@@ -2155,7 +2155,7 @@
         <v>153</v>
       </c>
       <c r="C60" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="D60" t="s">
         <v>157</v>
@@ -2169,7 +2169,7 @@
         <v>153</v>
       </c>
       <c r="C61" t="s">
-        <v>224</v>
+        <v>172</v>
       </c>
       <c r="D61" t="s">
         <v>157</v>
@@ -2183,7 +2183,7 @@
         <v>153</v>
       </c>
       <c r="C62" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="D62" t="s">
         <v>157</v>
@@ -2197,7 +2197,7 @@
         <v>152</v>
       </c>
       <c r="C63" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="D63" t="s">
         <v>157</v>
@@ -2211,7 +2211,7 @@
         <v>152</v>
       </c>
       <c r="C64" t="s">
-        <v>165</v>
+        <v>273</v>
       </c>
       <c r="D64" t="s">
         <v>157</v>
@@ -2225,7 +2225,7 @@
         <v>153</v>
       </c>
       <c r="C65" t="s">
-        <v>182</v>
+        <v>243</v>
       </c>
       <c r="D65" t="s">
         <v>157</v>
@@ -2239,7 +2239,7 @@
         <v>153</v>
       </c>
       <c r="C66" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
         <v>157</v>
@@ -2253,7 +2253,7 @@
         <v>152</v>
       </c>
       <c r="C67" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="D67" t="s">
         <v>156</v>
@@ -2267,7 +2267,7 @@
         <v>152</v>
       </c>
       <c r="C68" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="D68" t="s">
         <v>157</v>
@@ -2281,7 +2281,7 @@
         <v>153</v>
       </c>
       <c r="C69" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="D69" t="s">
         <v>156</v>
@@ -2295,7 +2295,7 @@
         <v>153</v>
       </c>
       <c r="C70" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="D70" t="s">
         <v>157</v>
@@ -2309,7 +2309,7 @@
         <v>153</v>
       </c>
       <c r="C71" t="s">
-        <v>268</v>
+        <v>240</v>
       </c>
       <c r="D71" t="s">
         <v>156</v>
@@ -2323,7 +2323,7 @@
         <v>152</v>
       </c>
       <c r="C72" t="s">
-        <v>273</v>
+        <v>237</v>
       </c>
       <c r="D72" t="s">
         <v>157</v>
@@ -2337,7 +2337,7 @@
         <v>153</v>
       </c>
       <c r="C73" t="s">
-        <v>207</v>
+        <v>247</v>
       </c>
       <c r="D73" t="s">
         <v>156</v>
@@ -2351,7 +2351,7 @@
         <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="D74" t="s">
         <v>157</v>
@@ -2365,7 +2365,7 @@
         <v>152</v>
       </c>
       <c r="C75" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="D75" t="s">
         <v>157</v>
@@ -2379,7 +2379,7 @@
         <v>152</v>
       </c>
       <c r="C76" t="s">
-        <v>166</v>
+        <v>280</v>
       </c>
       <c r="D76" t="s">
         <v>156</v>
@@ -2393,7 +2393,7 @@
         <v>152</v>
       </c>
       <c r="C77" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D77" t="s">
         <v>157</v>
@@ -2407,7 +2407,7 @@
         <v>152</v>
       </c>
       <c r="C78" t="s">
-        <v>181</v>
+        <v>266</v>
       </c>
       <c r="D78" t="s">
         <v>157</v>
@@ -2421,7 +2421,7 @@
         <v>152</v>
       </c>
       <c r="C79" t="s">
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="D79" t="s">
         <v>157</v>
@@ -2435,7 +2435,7 @@
         <v>153</v>
       </c>
       <c r="C80" t="s">
-        <v>263</v>
+        <v>168</v>
       </c>
       <c r="D80" t="s">
         <v>156</v>
@@ -2449,7 +2449,7 @@
         <v>153</v>
       </c>
       <c r="C81" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D81" t="s">
         <v>156</v>
@@ -2463,7 +2463,7 @@
         <v>152</v>
       </c>
       <c r="C82" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="D82" t="s">
         <v>156</v>
@@ -2477,7 +2477,7 @@
         <v>153</v>
       </c>
       <c r="C83" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="D83" t="s">
         <v>156</v>
@@ -2491,7 +2491,7 @@
         <v>152</v>
       </c>
       <c r="C84" t="s">
-        <v>276</v>
+        <v>228</v>
       </c>
       <c r="D84" t="s">
         <v>156</v>
@@ -2505,7 +2505,7 @@
         <v>153</v>
       </c>
       <c r="C85" t="s">
-        <v>248</v>
+        <v>304</v>
       </c>
       <c r="D85" t="s">
         <v>156</v>
@@ -2519,7 +2519,7 @@
         <v>153</v>
       </c>
       <c r="C86" t="s">
-        <v>172</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
         <v>157</v>
@@ -2533,7 +2533,7 @@
         <v>152</v>
       </c>
       <c r="C87" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="D87" t="s">
         <v>157</v>
@@ -2547,7 +2547,7 @@
         <v>153</v>
       </c>
       <c r="C88" t="s">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="D88" t="s">
         <v>157</v>
@@ -2561,7 +2561,7 @@
         <v>152</v>
       </c>
       <c r="C89" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D89" t="s">
         <v>157</v>
@@ -2575,7 +2575,7 @@
         <v>153</v>
       </c>
       <c r="C90" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="D90" t="s">
         <v>157</v>
@@ -2589,7 +2589,7 @@
         <v>153</v>
       </c>
       <c r="C91" t="s">
-        <v>180</v>
+        <v>220</v>
       </c>
       <c r="D91" t="s">
         <v>157</v>
@@ -2603,7 +2603,7 @@
         <v>153</v>
       </c>
       <c r="C92" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D92" t="s">
         <v>157</v>
@@ -2617,7 +2617,7 @@
         <v>152</v>
       </c>
       <c r="C93" t="s">
-        <v>170</v>
+        <v>307</v>
       </c>
       <c r="D93" t="s">
         <v>156</v>
@@ -2631,7 +2631,7 @@
         <v>153</v>
       </c>
       <c r="C94" t="s">
-        <v>212</v>
+        <v>161</v>
       </c>
       <c r="D94" t="s">
         <v>156</v>
@@ -2645,7 +2645,7 @@
         <v>153</v>
       </c>
       <c r="C95" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="D95" t="s">
         <v>157</v>
@@ -2659,7 +2659,7 @@
         <v>153</v>
       </c>
       <c r="C96" t="s">
-        <v>195</v>
+        <v>223</v>
       </c>
       <c r="D96" t="s">
         <v>156</v>
@@ -2673,7 +2673,7 @@
         <v>152</v>
       </c>
       <c r="C97" t="s">
-        <v>201</v>
+        <v>272</v>
       </c>
       <c r="D97" t="s">
         <v>156</v>
@@ -2687,7 +2687,7 @@
         <v>152</v>
       </c>
       <c r="C98" t="s">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="D98" t="s">
         <v>157</v>
@@ -2701,7 +2701,7 @@
         <v>152</v>
       </c>
       <c r="C99" t="s">
-        <v>160</v>
+        <v>265</v>
       </c>
       <c r="D99" t="s">
         <v>156</v>
@@ -2715,7 +2715,7 @@
         <v>152</v>
       </c>
       <c r="C100" t="s">
-        <v>281</v>
+        <v>248</v>
       </c>
       <c r="D100" t="s">
         <v>157</v>
@@ -2729,7 +2729,7 @@
         <v>153</v>
       </c>
       <c r="C101" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="D101" t="s">
         <v>157</v>
@@ -2743,7 +2743,7 @@
         <v>152</v>
       </c>
       <c r="C102" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="D102" t="s">
         <v>157</v>
@@ -2757,7 +2757,7 @@
         <v>153</v>
       </c>
       <c r="C103" t="s">
-        <v>193</v>
+        <v>222</v>
       </c>
       <c r="D103" t="s">
         <v>156</v>
@@ -2771,7 +2771,7 @@
         <v>152</v>
       </c>
       <c r="C104" t="s">
-        <v>192</v>
+        <v>255</v>
       </c>
       <c r="D104" t="s">
         <v>156</v>
@@ -2785,7 +2785,7 @@
         <v>153</v>
       </c>
       <c r="C105" t="s">
-        <v>159</v>
+        <v>213</v>
       </c>
       <c r="D105" t="s">
         <v>156</v>
@@ -2799,7 +2799,7 @@
         <v>153</v>
       </c>
       <c r="C106" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="D106" t="s">
         <v>156</v>
@@ -2813,7 +2813,7 @@
         <v>152</v>
       </c>
       <c r="C107" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="D107" t="s">
         <v>156</v>
@@ -2827,7 +2827,7 @@
         <v>152</v>
       </c>
       <c r="C108" t="s">
-        <v>218</v>
+        <v>264</v>
       </c>
       <c r="D108" t="s">
         <v>157</v>
@@ -2841,7 +2841,7 @@
         <v>152</v>
       </c>
       <c r="C109" t="s">
-        <v>236</v>
+        <v>174</v>
       </c>
       <c r="D109" t="s">
         <v>157</v>
@@ -2855,7 +2855,7 @@
         <v>153</v>
       </c>
       <c r="C110" t="s">
-        <v>185</v>
+        <v>231</v>
       </c>
       <c r="D110" t="s">
         <v>156</v>
@@ -2869,7 +2869,7 @@
         <v>152</v>
       </c>
       <c r="C111" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D111" t="s">
         <v>157</v>
@@ -2883,7 +2883,7 @@
         <v>152</v>
       </c>
       <c r="C112" t="s">
-        <v>285</v>
+        <v>192</v>
       </c>
       <c r="D112" t="s">
         <v>157</v>
@@ -2897,7 +2897,7 @@
         <v>152</v>
       </c>
       <c r="C113" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="D113" t="s">
         <v>157</v>
@@ -2911,7 +2911,7 @@
         <v>152</v>
       </c>
       <c r="C114" t="s">
-        <v>287</v>
+        <v>225</v>
       </c>
       <c r="D114" t="s">
         <v>157</v>
@@ -2925,7 +2925,7 @@
         <v>152</v>
       </c>
       <c r="C115" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D115" t="s">
         <v>157</v>
@@ -2939,7 +2939,7 @@
         <v>153</v>
       </c>
       <c r="C116" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="D116" t="s">
         <v>157</v>
@@ -2953,7 +2953,7 @@
         <v>152</v>
       </c>
       <c r="C117" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="D117" t="s">
         <v>157</v>
@@ -2967,7 +2967,7 @@
         <v>153</v>
       </c>
       <c r="C118" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="D118" t="s">
         <v>157</v>
@@ -2981,7 +2981,7 @@
         <v>153</v>
       </c>
       <c r="C119" t="s">
-        <v>270</v>
+        <v>226</v>
       </c>
       <c r="D119" t="s">
         <v>157</v>
@@ -2995,7 +2995,7 @@
         <v>153</v>
       </c>
       <c r="C120" t="s">
-        <v>306</v>
+        <v>182</v>
       </c>
       <c r="D120" t="s">
         <v>156</v>
@@ -3009,7 +3009,7 @@
         <v>153</v>
       </c>
       <c r="C121" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="D121" t="s">
         <v>157</v>
@@ -3023,7 +3023,7 @@
         <v>152</v>
       </c>
       <c r="C122" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D122" t="s">
         <v>156</v>
@@ -3037,7 +3037,7 @@
         <v>153</v>
       </c>
       <c r="C123" t="s">
-        <v>307</v>
+        <v>206</v>
       </c>
       <c r="D123" t="s">
         <v>156</v>
@@ -3051,7 +3051,7 @@
         <v>153</v>
       </c>
       <c r="C124" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D124" t="s">
         <v>156</v>
@@ -3065,7 +3065,7 @@
         <v>152</v>
       </c>
       <c r="C125" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="D125" t="s">
         <v>157</v>
@@ -3079,7 +3079,7 @@
         <v>152</v>
       </c>
       <c r="C126" t="s">
-        <v>198</v>
+        <v>233</v>
       </c>
       <c r="D126" t="s">
         <v>157</v>
@@ -3093,7 +3093,7 @@
         <v>153</v>
       </c>
       <c r="C127" t="s">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="D127" t="s">
         <v>157</v>
@@ -3107,7 +3107,7 @@
         <v>152</v>
       </c>
       <c r="C128" t="s">
-        <v>294</v>
+        <v>169</v>
       </c>
       <c r="D128" t="s">
         <v>156</v>
@@ -3121,7 +3121,7 @@
         <v>153</v>
       </c>
       <c r="C129" t="s">
-        <v>213</v>
+        <v>306</v>
       </c>
       <c r="D129" t="s">
         <v>156</v>
@@ -3135,7 +3135,7 @@
         <v>152</v>
       </c>
       <c r="C130" t="s">
-        <v>295</v>
+        <v>219</v>
       </c>
       <c r="D130" t="s">
         <v>156</v>
@@ -3149,7 +3149,7 @@
         <v>153</v>
       </c>
       <c r="C131" t="s">
-        <v>164</v>
+        <v>221</v>
       </c>
       <c r="D131" t="s">
         <v>157</v>
@@ -3163,7 +3163,7 @@
         <v>152</v>
       </c>
       <c r="C132" t="s">
-        <v>296</v>
+        <v>270</v>
       </c>
       <c r="D132" t="s">
         <v>156</v>
@@ -3177,7 +3177,7 @@
         <v>152</v>
       </c>
       <c r="C133" t="s">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="D133" t="s">
         <v>157</v>
@@ -3191,7 +3191,7 @@
         <v>152</v>
       </c>
       <c r="C134" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="D134" t="s">
         <v>157</v>
@@ -3205,7 +3205,7 @@
         <v>153</v>
       </c>
       <c r="C135" t="s">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="D135" t="s">
         <v>156</v>
@@ -3219,7 +3219,7 @@
         <v>152</v>
       </c>
       <c r="C136" t="s">
-        <v>297</v>
+        <v>171</v>
       </c>
       <c r="D136" t="s">
         <v>156</v>
@@ -3233,7 +3233,7 @@
         <v>153</v>
       </c>
       <c r="C137" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D137" t="s">
         <v>157</v>
@@ -3247,7 +3247,7 @@
         <v>152</v>
       </c>
       <c r="C138" t="s">
-        <v>298</v>
+        <v>165</v>
       </c>
       <c r="D138" t="s">
         <v>156</v>
@@ -3261,7 +3261,7 @@
         <v>153</v>
       </c>
       <c r="C139" t="s">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="D139" t="s">
         <v>156</v>
@@ -3275,7 +3275,7 @@
         <v>152</v>
       </c>
       <c r="C140" t="s">
-        <v>299</v>
+        <v>278</v>
       </c>
       <c r="D140" t="s">
         <v>157</v>
@@ -3289,7 +3289,7 @@
         <v>152</v>
       </c>
       <c r="C141" t="s">
-        <v>300</v>
+        <v>198</v>
       </c>
       <c r="D141" t="s">
         <v>156</v>
@@ -3303,7 +3303,7 @@
         <v>153</v>
       </c>
       <c r="C142" t="s">
-        <v>239</v>
+        <v>305</v>
       </c>
       <c r="D142" t="s">
         <v>156</v>
@@ -3317,7 +3317,7 @@
         <v>153</v>
       </c>
       <c r="C143" t="s">
-        <v>232</v>
+        <v>288</v>
       </c>
       <c r="D143" t="s">
         <v>157</v>
@@ -3331,7 +3331,7 @@
         <v>153</v>
       </c>
       <c r="C144" t="s">
-        <v>199</v>
+        <v>175</v>
       </c>
       <c r="D144" t="s">
         <v>157</v>
@@ -3345,7 +3345,7 @@
         <v>152</v>
       </c>
       <c r="C145" t="s">
-        <v>301</v>
+        <v>279</v>
       </c>
       <c r="D145" t="s">
         <v>156</v>
@@ -3359,7 +3359,7 @@
         <v>153</v>
       </c>
       <c r="C146" t="s">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="D146" t="s">
         <v>156</v>
@@ -3373,7 +3373,7 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>227</v>
+        <v>208</v>
       </c>
       <c r="D147" t="s">
         <v>156</v>
@@ -3387,7 +3387,7 @@
         <v>153</v>
       </c>
       <c r="C148" t="s">
-        <v>289</v>
+        <v>229</v>
       </c>
       <c r="D148" t="s">
         <v>157</v>
@@ -3401,7 +3401,7 @@
         <v>152</v>
       </c>
       <c r="C149" t="s">
-        <v>229</v>
+        <v>170</v>
       </c>
       <c r="D149" t="s">
         <v>156</v>
@@ -3415,7 +3415,7 @@
         <v>152</v>
       </c>
       <c r="C150" t="s">
-        <v>303</v>
+        <v>217</v>
       </c>
       <c r="D150" t="s">
         <v>157</v>
@@ -3429,7 +3429,7 @@
         <v>153</v>
       </c>
       <c r="C151" t="s">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="D151" t="s">
         <v>156</v>
